--- a/all_points_test.xlsx
+++ b/all_points_test.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="19200" windowHeight="8055"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,13 +41,13 @@
     <t>totalDemand</t>
   </si>
   <si>
-    <t>selfDemand</t>
-  </si>
-  <si>
-    <t>depotDemand</t>
-  </si>
-  <si>
-    <t>deliverDemand</t>
+    <t>pop</t>
+  </si>
+  <si>
+    <t>calDemand</t>
+  </si>
+  <si>
+    <t>totalDemandcal</t>
   </si>
   <si>
     <t>[66, 29, -37]</t>
@@ -147,19 +147,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.8"/>
-      <color rgb="FFC77DBB"/>
-      <name val="Courier New"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -626,144 +620,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1293,9 +1284,6 @@
   <sheetPr/>
   <dimension ref="A1:G30"/>
   <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="6"/>
-  <cols>
-    <col min="2" max="3" width="12.7964601769912"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -1307,16 +1295,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1330,17 +1318,19 @@
       <c r="C2">
         <v>31.29026052</v>
       </c>
-      <c r="D2" s="1">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1">
-        <v>3</v>
-      </c>
-      <c r="G2" s="1">
-        <v>2</v>
+      <c r="D2">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E2">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F2">
+        <f t="shared" ref="F2:F30" si="0">E2*34750*3500/116409</f>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G2">
+        <f t="shared" ref="G2:G30" si="1">F2/2506*3500</f>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1353,17 +1343,19 @@
       <c r="C3">
         <v>31.29026052</v>
       </c>
-      <c r="D3" s="1">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="1">
-        <v>3</v>
-      </c>
-      <c r="G3" s="1">
-        <v>2</v>
+      <c r="D3">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E3">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1376,17 +1368,19 @@
       <c r="C4">
         <v>31.29181819</v>
       </c>
-      <c r="D4" s="1">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3</v>
-      </c>
-      <c r="G4" s="1">
-        <v>2</v>
+      <c r="D4">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E4">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1399,17 +1393,19 @@
       <c r="C5">
         <v>31.29181819</v>
       </c>
-      <c r="D5" s="1">
-        <v>6</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>3</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2</v>
+      <c r="D5">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E5">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1422,17 +1418,19 @@
       <c r="C6">
         <v>31.29181819</v>
       </c>
-      <c r="D6" s="1">
-        <v>6</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
+      <c r="D6">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E6">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1445,17 +1443,19 @@
       <c r="C7">
         <v>31.29181819</v>
       </c>
-      <c r="D7" s="1">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>3</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2</v>
+      <c r="D7">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E7">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1468,17 +1468,19 @@
       <c r="C8">
         <v>31.29337586</v>
       </c>
-      <c r="D8" s="1">
-        <v>6</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3</v>
-      </c>
-      <c r="G8" s="1">
-        <v>2</v>
+      <c r="D8">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E8">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1491,17 +1493,19 @@
       <c r="C9">
         <v>31.29337586</v>
       </c>
-      <c r="D9" s="1">
-        <v>6</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1">
-        <v>2</v>
+      <c r="D9">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E9">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1514,17 +1518,19 @@
       <c r="C10">
         <v>31.29493353</v>
       </c>
-      <c r="D10" s="1">
-        <v>6</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1">
-        <v>2</v>
+      <c r="D10">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E10">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="1"/>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1537,17 +1543,19 @@
       <c r="C11">
         <v>31.29493353</v>
       </c>
-      <c r="D11" s="1">
-        <v>6</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>2</v>
+      <c r="D11">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E11">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="1"/>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1560,17 +1568,19 @@
       <c r="C12">
         <v>31.29493353</v>
       </c>
-      <c r="D12" s="1">
-        <v>6</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>3</v>
-      </c>
-      <c r="G12" s="1">
-        <v>2</v>
+      <c r="D12">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E12">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1583,17 +1593,19 @@
       <c r="C13">
         <v>31.29493353</v>
       </c>
-      <c r="D13" s="1">
-        <v>6</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1">
-        <v>2</v>
+      <c r="D13">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E13">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1606,17 +1618,19 @@
       <c r="C14">
         <v>31.2964912</v>
       </c>
-      <c r="D14" s="1">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1">
-        <v>2</v>
+      <c r="D14">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E14">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1629,17 +1643,19 @@
       <c r="C15">
         <v>31.2964912</v>
       </c>
-      <c r="D15" s="1">
-        <v>6</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>3</v>
-      </c>
-      <c r="G15" s="1">
-        <v>2</v>
+      <c r="D15">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E15">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1652,17 +1668,19 @@
       <c r="C16">
         <v>31.29804887</v>
       </c>
-      <c r="D16" s="1">
-        <v>6</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>3</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2</v>
+      <c r="D16">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E16">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1675,17 +1693,19 @@
       <c r="C17">
         <v>31.29804887</v>
       </c>
-      <c r="D17" s="1">
-        <v>6</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2</v>
+      <c r="D17">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E17">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="1"/>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1698,17 +1718,19 @@
       <c r="C18">
         <v>31.29804887</v>
       </c>
-      <c r="D18" s="1">
-        <v>6</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>3</v>
-      </c>
-      <c r="G18" s="1">
-        <v>2</v>
+      <c r="D18">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E18">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1721,17 +1743,19 @@
       <c r="C19">
         <v>31.29804887</v>
       </c>
-      <c r="D19" s="1">
-        <v>6</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>3</v>
-      </c>
-      <c r="G19" s="1">
-        <v>2</v>
+      <c r="D19">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E19">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1744,17 +1768,19 @@
       <c r="C20">
         <v>31.25443412</v>
       </c>
-      <c r="D20" s="1">
-        <v>6</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>3</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
+      <c r="D20">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E20">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1767,17 +1793,19 @@
       <c r="C21">
         <v>31.25443412</v>
       </c>
-      <c r="D21" s="1">
-        <v>6</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>3</v>
-      </c>
-      <c r="G21" s="1">
-        <v>2</v>
+      <c r="D21">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E21">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1790,17 +1818,19 @@
       <c r="C22">
         <v>31.25443412</v>
       </c>
-      <c r="D22" s="1">
-        <v>6</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>3</v>
-      </c>
-      <c r="G22" s="1">
-        <v>2</v>
+      <c r="D22">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E22">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="1"/>
+        <v>4.41705286278476</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1813,17 +1843,19 @@
       <c r="C23">
         <v>31.25599179</v>
       </c>
-      <c r="D23" s="1">
-        <v>6</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>3</v>
-      </c>
-      <c r="G23" s="1">
-        <v>2</v>
+      <c r="D23">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E23">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="1"/>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1836,17 +1868,19 @@
       <c r="C24">
         <v>31.25599179</v>
       </c>
-      <c r="D24" s="1">
-        <v>6</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>3</v>
-      </c>
-      <c r="G24" s="1">
-        <v>2</v>
+      <c r="D24">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E24">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1859,17 +1893,19 @@
       <c r="C25">
         <v>31.25599179</v>
       </c>
-      <c r="D25" s="1">
-        <v>6</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>3</v>
-      </c>
-      <c r="G25" s="1">
-        <v>2</v>
+      <c r="D25">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E25">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="1"/>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1882,17 +1918,19 @@
       <c r="C26">
         <v>31.25754946</v>
       </c>
-      <c r="D26" s="1">
-        <v>6</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>3</v>
-      </c>
-      <c r="G26" s="1">
-        <v>2</v>
+      <c r="D26">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E26">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1905,17 +1943,19 @@
       <c r="C27">
         <v>31.25754946</v>
       </c>
-      <c r="D27" s="1">
-        <v>6</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>3</v>
-      </c>
-      <c r="G27" s="1">
-        <v>2</v>
+      <c r="D27">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E27">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1928,17 +1968,19 @@
       <c r="C28">
         <v>31.25910713</v>
       </c>
-      <c r="D28" s="1">
-        <v>6</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>3</v>
-      </c>
-      <c r="G28" s="1">
-        <v>2</v>
+      <c r="D28">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E28">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="1"/>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1951,17 +1993,19 @@
       <c r="C29">
         <v>31.25910713</v>
       </c>
-      <c r="D29" s="1">
-        <v>6</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>3</v>
-      </c>
-      <c r="G29" s="1">
-        <v>2</v>
+      <c r="D29">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E29">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="1"/>
+        <v>4.41705286278476</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1974,17 +2018,19 @@
       <c r="C30">
         <v>31.25910713</v>
       </c>
-      <c r="D30" s="1">
-        <v>6</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>3</v>
-      </c>
-      <c r="G30" s="1">
-        <v>2</v>
+      <c r="D30">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E30">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="1"/>
+        <v>2.33156603027792</v>
       </c>
     </row>
   </sheetData>

--- a/all_points_test.xlsx
+++ b/all_points_test.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1283,7 +1283,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -1301,7 +1301,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1312,23 +1312,23 @@
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <v>121.194746</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>31.29026052</v>
       </c>
-      <c r="D2">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E2">
+      <c r="D2" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E2" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <f t="shared" ref="F2:F30" si="0">E2*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <f t="shared" ref="G2:G30" si="1">F2/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
@@ -1337,23 +1337,23 @@
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <v>121.2052685</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>31.29026052</v>
       </c>
-      <c r="D3">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E3">
+      <c r="D3" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E3" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1362,23 +1362,23 @@
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <v>121.1936937</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>31.29181819</v>
       </c>
-      <c r="D4">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E4">
+      <c r="D4" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E4" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1387,23 +1387,23 @@
       <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <v>121.1957982</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>31.29181819</v>
       </c>
-      <c r="D5">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E5">
+      <c r="D5" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E5" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1412,23 +1412,23 @@
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <v>121.1979027</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>31.29181819</v>
       </c>
-      <c r="D6">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E6">
+      <c r="D6" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E6" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1437,23 +1437,23 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="1">
         <v>121.2063207</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>31.29181819</v>
       </c>
-      <c r="D7">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E7">
+      <c r="D7" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E7" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1462,23 +1462,23 @@
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="1">
         <v>121.198955</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>31.29337586</v>
       </c>
-      <c r="D8">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E8">
+      <c r="D8" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E8" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1487,23 +1487,23 @@
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="1">
         <v>121.2010595</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>31.29337586</v>
       </c>
-      <c r="D9">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E9">
+      <c r="D9" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E9" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1512,23 +1512,23 @@
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="1">
         <v>121.1979027</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>31.29493353</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
         <v>2.33156603027792</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="1">
         <v>0.00159780746831107</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <f t="shared" si="0"/>
         <v>1.66940127767899</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <f t="shared" si="1"/>
         <v>2.33156603027792</v>
       </c>
@@ -1537,23 +1537,23 @@
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="1">
         <v>121.2000072</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>31.29493353</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>2.33156603027792</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="1">
         <v>0.00159780746831107</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <f t="shared" si="0"/>
         <v>1.66940127767899</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <f t="shared" si="1"/>
         <v>2.33156603027792</v>
       </c>
@@ -1562,23 +1562,23 @@
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="1">
         <v>121.2021117</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>31.29493353</v>
       </c>
-      <c r="D12">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E12">
+      <c r="D12" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E12" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1587,23 +1587,23 @@
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="1">
         <v>121.2084252</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>31.29493353</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1612,23 +1612,23 @@
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="1">
         <v>121.2010595</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>31.2964912</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1637,23 +1637,23 @@
       <c r="A15" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="1">
         <v>121.203164</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>31.2964912</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1662,23 +1662,23 @@
       <c r="A16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="1">
         <v>121.1957982</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>31.29804887</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1687,23 +1687,23 @@
       <c r="A17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="1">
         <v>121.2000072</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="1">
         <v>31.29804887</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
         <v>2.33156603027792</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="1">
         <v>0.00159780746831107</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="1">
         <f t="shared" si="0"/>
         <v>1.66940127767899</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <f t="shared" si="1"/>
         <v>2.33156603027792</v>
       </c>
@@ -1712,23 +1712,23 @@
       <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="1">
         <v>121.2021117</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="1">
         <v>31.29804887</v>
       </c>
-      <c r="D18">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E18">
+      <c r="D18" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E18" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1737,23 +1737,23 @@
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="1">
         <v>121.2042162</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="1">
         <v>31.29804887</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1762,23 +1762,23 @@
       <c r="A20" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="1">
         <v>121.1957982</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="1">
         <v>31.25443412</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1787,23 +1787,23 @@
       <c r="A21" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="1">
         <v>121.2021117</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="1">
         <v>31.25443412</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1812,23 +1812,23 @@
       <c r="A22" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="1">
         <v>121.2042162</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="1">
         <v>31.25443412</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
         <v>4.41705286278476</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="1">
         <v>0.00302697841726619</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="1">
         <f t="shared" si="0"/>
         <v>3.16260984975389</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <f t="shared" si="1"/>
         <v>4.41705286278476</v>
       </c>
@@ -1837,23 +1837,23 @@
       <c r="A23" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="1">
         <v>121.1926415</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="1">
         <v>31.25599179</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
         <v>2.33156603027792</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="1">
         <v>0.00159780746831107</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="1">
         <f t="shared" si="0"/>
         <v>1.66940127767899</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <f t="shared" si="1"/>
         <v>2.33156603027792</v>
       </c>
@@ -1862,23 +1862,23 @@
       <c r="A24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="1">
         <v>121.198955</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="1">
         <v>31.25599179</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
         <v>2.33156603027792</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="1">
         <v>0.00159780746831107</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="1">
         <f t="shared" si="0"/>
         <v>1.66940127767899</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <f t="shared" si="1"/>
         <v>2.33156603027792</v>
       </c>
@@ -1887,23 +1887,23 @@
       <c r="A25" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="1">
         <v>121.2010595</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="1">
         <v>31.25599179</v>
       </c>
-      <c r="D25">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E25">
+      <c r="D25" s="1">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E25" s="1">
         <v>0.00133167948399901</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <f t="shared" si="0"/>
         <v>1.39134875517683</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <f t="shared" si="1"/>
         <v>1.94322451840339</v>
       </c>
@@ -1912,23 +1912,23 @@
       <c r="A26" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="1">
         <v>121.2000072</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="1">
         <v>31.25754946</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1937,23 +1937,23 @@
       <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="1">
         <v>121.2147387</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="1">
         <v>31.25754946</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1962,23 +1962,23 @@
       <c r="A28" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <v>121.1884325</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="1">
         <v>31.25910713</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
         <v>3.38153726789807</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="1">
         <v>0.00231734612310152</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="1">
         <f t="shared" si="0"/>
         <v>2.42118068381502</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <f t="shared" si="1"/>
         <v>3.38153726789807</v>
       </c>
@@ -1987,23 +1987,23 @@
       <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="1">
         <v>121.2010595</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="1">
         <v>31.25910713</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
         <v>4.41705286278476</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="1">
         <v>0.00302697841726619</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="1">
         <f t="shared" si="0"/>
         <v>3.16260984975389</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <f t="shared" si="1"/>
         <v>4.41705286278476</v>
       </c>
@@ -2012,23 +2012,23 @@
       <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="1">
         <v>121.203164</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="1">
         <v>31.25910713</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
         <v>2.33156603027792</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="1">
         <v>0.00159780746831107</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="1">
         <f t="shared" si="0"/>
         <v>1.66940127767899</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <f t="shared" si="1"/>
         <v>2.33156603027792</v>
       </c>

--- a/all_points_test.xlsx
+++ b/all_points_test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Gridid</t>
   </si>
@@ -77,15 +77,9 @@
     <t>[19, 4, -15]</t>
   </si>
   <si>
-    <t>[21, 5, -16]</t>
-  </si>
-  <si>
     <t>[23, 6, -17]</t>
   </si>
   <si>
-    <t>[25, 7, -18]</t>
-  </si>
-  <si>
     <t>[27, 8, -19]</t>
   </si>
   <si>
@@ -99,9 +93,6 @@
   </si>
   <si>
     <t>[35, 12, -23]</t>
-  </si>
-  <si>
-    <t>[37, 13, -24]</t>
   </si>
   <si>
     <t>[39, 14, -25]</t>
@@ -1282,8 +1273,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelCol="6"/>
+  <dimension ref="A1:G27"/>
+  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="12.625"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
@@ -1325,11 +1319,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F2" s="1">
-        <f t="shared" ref="F2:F30" si="0">E2*34750*3500/116409</f>
+        <f>E2*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G2" s="1">
-        <f t="shared" ref="G2:G30" si="1">F2/2506*3500</f>
+        <f>F2/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1350,11 +1344,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F3" s="1">
-        <f t="shared" si="0"/>
+        <f>E3*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G3" s="1">
-        <f t="shared" si="1"/>
+        <f>F3/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1375,11 +1369,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F4" s="1">
-        <f t="shared" si="0"/>
+        <f>E4*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G4" s="1">
-        <f t="shared" si="1"/>
+        <f>F4/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1400,11 +1394,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F5" s="1">
-        <f t="shared" si="0"/>
+        <f>E5*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G5" s="1">
-        <f t="shared" si="1"/>
+        <f>F5/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1425,11 +1419,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F6" s="1">
-        <f t="shared" si="0"/>
+        <f>E6*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G6" s="1">
-        <f t="shared" si="1"/>
+        <f>F6/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1450,11 +1444,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F7" s="1">
-        <f t="shared" si="0"/>
+        <f>E7*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G7" s="1">
-        <f t="shared" si="1"/>
+        <f>F7/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1475,11 +1469,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F8" s="1">
-        <f t="shared" si="0"/>
+        <f>E8*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G8" s="1">
-        <f t="shared" si="1"/>
+        <f>F8/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1500,11 +1494,11 @@
         <v>0.00133167948399901</v>
       </c>
       <c r="F9" s="1">
-        <f t="shared" si="0"/>
+        <f>E9*34750*3500/116409</f>
         <v>1.39134875517683</v>
       </c>
       <c r="G9" s="1">
-        <f t="shared" si="1"/>
+        <f>F9/2506*3500</f>
         <v>1.94322451840339</v>
       </c>
     </row>
@@ -1525,11 +1519,11 @@
         <v>0.00159780746831107</v>
       </c>
       <c r="F10" s="1">
-        <f t="shared" si="0"/>
+        <f>E10*34750*3500/116409</f>
         <v>1.66940127767899</v>
       </c>
       <c r="G10" s="1">
-        <f t="shared" si="1"/>
+        <f>F10/2506*3500</f>
         <v>2.33156603027792</v>
       </c>
     </row>
@@ -1538,24 +1532,24 @@
         <v>16</v>
       </c>
       <c r="B11" s="1">
-        <v>121.2000072</v>
+        <v>121.2021117</v>
       </c>
       <c r="C11" s="1">
         <v>31.29493353</v>
       </c>
       <c r="D11" s="1">
-        <v>2.33156603027792</v>
+        <v>1.94322451840339</v>
       </c>
       <c r="E11" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00133167948399901</v>
       </c>
       <c r="F11" s="1">
-        <f t="shared" si="0"/>
-        <v>1.66940127767899</v>
+        <f>E11*34750*3500/116409</f>
+        <v>1.39134875517683</v>
       </c>
       <c r="G11" s="1">
-        <f t="shared" si="1"/>
-        <v>2.33156603027792</v>
+        <f>F11/2506*3500</f>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1563,24 +1557,24 @@
         <v>17</v>
       </c>
       <c r="B12" s="1">
-        <v>121.2021117</v>
+        <v>121.2010595</v>
       </c>
       <c r="C12" s="1">
-        <v>31.29493353</v>
+        <v>31.2964912</v>
       </c>
       <c r="D12" s="1">
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E12" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" si="0"/>
-        <v>1.39134875517683</v>
+        <f t="shared" ref="F12:F28" si="0">E12*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" si="1"/>
-        <v>1.94322451840339</v>
+        <f t="shared" ref="G12:G28" si="1">F12/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1588,10 +1582,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>121.2084252</v>
+        <v>121.203164</v>
       </c>
       <c r="C13" s="1">
-        <v>31.29493353</v>
+        <v>31.2964912</v>
       </c>
       <c r="D13" s="1">
         <v>3.38153726789807</v>
@@ -1613,10 +1607,10 @@
         <v>19</v>
       </c>
       <c r="B14" s="1">
-        <v>121.2010595</v>
+        <v>121.1957982</v>
       </c>
       <c r="C14" s="1">
-        <v>31.2964912</v>
+        <v>31.29804887</v>
       </c>
       <c r="D14" s="1">
         <v>3.38153726789807</v>
@@ -1638,24 +1632,24 @@
         <v>20</v>
       </c>
       <c r="B15" s="1">
-        <v>121.203164</v>
+        <v>121.2000072</v>
       </c>
       <c r="C15" s="1">
-        <v>31.2964912</v>
+        <v>31.29804887</v>
       </c>
       <c r="D15" s="1">
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E15" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F15" s="1">
         <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <v>1.66940127767899</v>
       </c>
       <c r="G15" s="1">
         <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1663,24 +1657,24 @@
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>121.1957982</v>
+        <v>121.2021117</v>
       </c>
       <c r="C16" s="1">
         <v>31.29804887</v>
       </c>
       <c r="D16" s="1">
-        <v>3.38153726789807</v>
+        <v>1.94322451840339</v>
       </c>
       <c r="E16" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00133167948399901</v>
       </c>
       <c r="F16" s="1">
         <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <v>1.39134875517683</v>
       </c>
       <c r="G16" s="1">
         <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1688,24 +1682,24 @@
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>121.2000072</v>
+        <v>121.1957982</v>
       </c>
       <c r="C17" s="1">
-        <v>31.29804887</v>
+        <v>31.25443412</v>
       </c>
       <c r="D17" s="1">
-        <v>2.33156603027792</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E17" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F17" s="1">
-        <f t="shared" si="0"/>
-        <v>1.66940127767899</v>
+        <f>E17*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G17" s="1">
-        <f t="shared" si="1"/>
-        <v>2.33156603027792</v>
+        <f>F17/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1716,21 +1710,21 @@
         <v>121.2021117</v>
       </c>
       <c r="C18" s="1">
-        <v>31.29804887</v>
+        <v>31.25443412</v>
       </c>
       <c r="D18" s="1">
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E18" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F18" s="1">
-        <f t="shared" si="0"/>
-        <v>1.39134875517683</v>
+        <f>E18*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G18" s="1">
-        <f t="shared" si="1"/>
-        <v>1.94322451840339</v>
+        <f>F18/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1741,21 +1735,21 @@
         <v>121.2042162</v>
       </c>
       <c r="C19" s="1">
-        <v>31.29804887</v>
+        <v>31.25443412</v>
       </c>
       <c r="D19" s="1">
-        <v>3.38153726789807</v>
+        <v>4.41705286278476</v>
       </c>
       <c r="E19" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00302697841726619</v>
       </c>
       <c r="F19" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <f>E19*34750*3500/116409</f>
+        <v>3.16260984975389</v>
       </c>
       <c r="G19" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <f>F19/2506*3500</f>
+        <v>4.41705286278476</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1763,24 +1757,24 @@
         <v>25</v>
       </c>
       <c r="B20" s="1">
-        <v>121.1957982</v>
+        <v>121.1926415</v>
       </c>
       <c r="C20" s="1">
-        <v>31.25443412</v>
+        <v>31.25599179</v>
       </c>
       <c r="D20" s="1">
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E20" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F20" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <f>E20*34750*3500/116409</f>
+        <v>1.66940127767899</v>
       </c>
       <c r="G20" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <f>F20/2506*3500</f>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1788,24 +1782,24 @@
         <v>26</v>
       </c>
       <c r="B21" s="1">
-        <v>121.2021117</v>
+        <v>121.198955</v>
       </c>
       <c r="C21" s="1">
-        <v>31.25443412</v>
+        <v>31.25599179</v>
       </c>
       <c r="D21" s="1">
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E21" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F21" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <f>E21*34750*3500/116409</f>
+        <v>1.66940127767899</v>
       </c>
       <c r="G21" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <f>F21/2506*3500</f>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1813,24 +1807,24 @@
         <v>27</v>
       </c>
       <c r="B22" s="1">
-        <v>121.2042162</v>
+        <v>121.2010595</v>
       </c>
       <c r="C22" s="1">
-        <v>31.25443412</v>
+        <v>31.25599179</v>
       </c>
       <c r="D22" s="1">
-        <v>4.41705286278476</v>
+        <v>1.94322451840339</v>
       </c>
       <c r="E22" s="1">
-        <v>0.00302697841726619</v>
+        <v>0.00133167948399901</v>
       </c>
       <c r="F22" s="1">
-        <f t="shared" si="0"/>
-        <v>3.16260984975389</v>
+        <f>E22*34750*3500/116409</f>
+        <v>1.39134875517683</v>
       </c>
       <c r="G22" s="1">
-        <f t="shared" si="1"/>
-        <v>4.41705286278476</v>
+        <f>F22/2506*3500</f>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1838,24 +1832,24 @@
         <v>28</v>
       </c>
       <c r="B23" s="1">
-        <v>121.1926415</v>
+        <v>121.2000072</v>
       </c>
       <c r="C23" s="1">
-        <v>31.25599179</v>
+        <v>31.25754946</v>
       </c>
       <c r="D23" s="1">
-        <v>2.33156603027792</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E23" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F23" s="1">
-        <f t="shared" si="0"/>
-        <v>1.66940127767899</v>
+        <f>E23*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G23" s="1">
-        <f t="shared" si="1"/>
-        <v>2.33156603027792</v>
+        <f>F23/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1863,24 +1857,24 @@
         <v>29</v>
       </c>
       <c r="B24" s="1">
-        <v>121.198955</v>
+        <v>121.2147387</v>
       </c>
       <c r="C24" s="1">
-        <v>31.25599179</v>
+        <v>31.25754946</v>
       </c>
       <c r="D24" s="1">
-        <v>2.33156603027792</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E24" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F24" s="1">
-        <f t="shared" si="0"/>
-        <v>1.66940127767899</v>
+        <f>E24*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G24" s="1">
-        <f t="shared" si="1"/>
-        <v>2.33156603027792</v>
+        <f>F24/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1888,24 +1882,24 @@
         <v>30</v>
       </c>
       <c r="B25" s="1">
-        <v>121.2010595</v>
+        <v>121.1884325</v>
       </c>
       <c r="C25" s="1">
-        <v>31.25599179</v>
+        <v>31.25910713</v>
       </c>
       <c r="D25" s="1">
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E25" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F25" s="1">
-        <f t="shared" si="0"/>
-        <v>1.39134875517683</v>
+        <f>E25*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G25" s="1">
-        <f t="shared" si="1"/>
-        <v>1.94322451840339</v>
+        <f>F25/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1913,24 +1907,24 @@
         <v>31</v>
       </c>
       <c r="B26" s="1">
-        <v>121.2000072</v>
+        <v>121.2010595</v>
       </c>
       <c r="C26" s="1">
-        <v>31.25754946</v>
+        <v>31.25910713</v>
       </c>
       <c r="D26" s="1">
-        <v>3.38153726789807</v>
+        <v>4.41705286278476</v>
       </c>
       <c r="E26" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00302697841726619</v>
       </c>
       <c r="F26" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <f>E26*34750*3500/116409</f>
+        <v>3.16260984975389</v>
       </c>
       <c r="G26" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <f>F26/2506*3500</f>
+        <v>4.41705286278476</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1938,98 +1932,23 @@
         <v>32</v>
       </c>
       <c r="B27" s="1">
-        <v>121.2147387</v>
+        <v>121.203164</v>
       </c>
       <c r="C27" s="1">
-        <v>31.25754946</v>
+        <v>31.25910713</v>
       </c>
       <c r="D27" s="1">
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E27" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F27" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <f>E27*34750*3500/116409</f>
+        <v>1.66940127767899</v>
       </c>
       <c r="G27" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B28" s="1">
-        <v>121.1884325</v>
-      </c>
-      <c r="C28" s="1">
-        <v>31.25910713</v>
-      </c>
-      <c r="D28" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E28" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F28" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G28" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="1">
-        <v>121.2010595</v>
-      </c>
-      <c r="C29" s="1">
-        <v>31.25910713</v>
-      </c>
-      <c r="D29" s="1">
-        <v>4.41705286278476</v>
-      </c>
-      <c r="E29" s="1">
-        <v>0.00302697841726619</v>
-      </c>
-      <c r="F29" s="1">
-        <f t="shared" si="0"/>
-        <v>3.16260984975389</v>
-      </c>
-      <c r="G29" s="1">
-        <f t="shared" si="1"/>
-        <v>4.41705286278476</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="1">
-        <v>121.203164</v>
-      </c>
-      <c r="C30" s="1">
-        <v>31.25910713</v>
-      </c>
-      <c r="D30" s="1">
-        <v>2.33156603027792</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0.00159780746831107</v>
-      </c>
-      <c r="F30" s="1">
-        <f t="shared" si="0"/>
-        <v>1.66940127767899</v>
-      </c>
-      <c r="G30" s="1">
-        <f t="shared" si="1"/>
+        <f>F27/2506*3500</f>
         <v>2.33156603027792</v>
       </c>
     </row>

--- a/all_points_test.xlsx
+++ b/all_points_test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="19200" windowHeight="8055"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Gridid</t>
   </si>
@@ -56,15 +56,9 @@
     <t>[68, 30, -38]</t>
   </si>
   <si>
-    <t>[70, 31, -39]</t>
-  </si>
-  <si>
     <t>[7, -2, -9]</t>
   </si>
   <si>
-    <t>[9, -1, -10]</t>
-  </si>
-  <si>
     <t>[11, 0, -11]</t>
   </si>
   <si>
@@ -74,10 +68,7 @@
     <t>[17, 3, -14]</t>
   </si>
   <si>
-    <t>[19, 4, -15]</t>
-  </si>
-  <si>
-    <t>[23, 6, -17]</t>
+    <t>[25, 7, -18]</t>
   </si>
   <si>
     <t>[27, 8, -19]</t>
@@ -101,31 +92,19 @@
     <t>[41, 15, -26]</t>
   </si>
   <si>
-    <t>[43, 16, -27]</t>
-  </si>
-  <si>
     <t>[47, 18, -29]</t>
   </si>
   <si>
     <t>[49, 19, -30]</t>
   </si>
   <si>
-    <t>[51, 20, -31]</t>
-  </si>
-  <si>
     <t>[53, 21, -32]</t>
   </si>
   <si>
     <t>[55, 22, -33]</t>
   </si>
   <si>
-    <t>[57, 23, -34]</t>
-  </si>
-  <si>
     <t>[59, 24, -35]</t>
-  </si>
-  <si>
-    <t>[61, 25, -36]</t>
   </si>
 </sst>
 </file>
@@ -1273,10 +1252,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="8.72566371681416" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="7" width="12.625"/>
+    <col min="2" max="7" width="12.7964601769912"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1357,7 +1336,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="1">
-        <v>121.1936937</v>
+        <v>121.1957982</v>
       </c>
       <c r="C4" s="1">
         <v>31.29181819</v>
@@ -1382,7 +1361,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="1">
-        <v>121.1957982</v>
+        <v>121.2063207</v>
       </c>
       <c r="C5" s="1">
         <v>31.29181819</v>
@@ -1407,10 +1386,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="1">
-        <v>121.1979027</v>
+        <v>121.198955</v>
       </c>
       <c r="C6" s="1">
-        <v>31.29181819</v>
+        <v>31.29337586</v>
       </c>
       <c r="D6" s="1">
         <v>1.94322451840339</v>
@@ -1432,10 +1411,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>121.2063207</v>
+        <v>121.2010595</v>
       </c>
       <c r="C7" s="1">
-        <v>31.29181819</v>
+        <v>31.29337586</v>
       </c>
       <c r="D7" s="1">
         <v>1.94322451840339</v>
@@ -1457,24 +1436,24 @@
         <v>13</v>
       </c>
       <c r="B8" s="1">
-        <v>121.198955</v>
+        <v>121.2084252</v>
       </c>
       <c r="C8" s="1">
-        <v>31.29337586</v>
+        <v>31.29493353</v>
       </c>
       <c r="D8" s="1">
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E8" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F8" s="1">
         <f>E8*34750*3500/116409</f>
-        <v>1.39134875517683</v>
+        <v>2.42118068381502</v>
       </c>
       <c r="G8" s="1">
         <f>F8/2506*3500</f>
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1485,21 +1464,21 @@
         <v>121.2010595</v>
       </c>
       <c r="C9" s="1">
-        <v>31.29337586</v>
+        <v>31.2964912</v>
       </c>
       <c r="D9" s="1">
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E9" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F9" s="1">
         <f>E9*34750*3500/116409</f>
-        <v>1.39134875517683</v>
+        <v>2.42118068381502</v>
       </c>
       <c r="G9" s="1">
         <f>F9/2506*3500</f>
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1507,24 +1486,24 @@
         <v>15</v>
       </c>
       <c r="B10" s="1">
-        <v>121.1979027</v>
+        <v>121.203164</v>
       </c>
       <c r="C10" s="1">
-        <v>31.29493353</v>
+        <v>31.2964912</v>
       </c>
       <c r="D10" s="1">
-        <v>2.33156603027792</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E10" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F10" s="1">
         <f>E10*34750*3500/116409</f>
-        <v>1.66940127767899</v>
+        <v>2.42118068381502</v>
       </c>
       <c r="G10" s="1">
         <f>F10/2506*3500</f>
-        <v>2.33156603027792</v>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1532,24 +1511,24 @@
         <v>16</v>
       </c>
       <c r="B11" s="1">
-        <v>121.2021117</v>
+        <v>121.1957982</v>
       </c>
       <c r="C11" s="1">
-        <v>31.29493353</v>
+        <v>31.29804887</v>
       </c>
       <c r="D11" s="1">
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E11" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F11" s="1">
         <f>E11*34750*3500/116409</f>
-        <v>1.39134875517683</v>
+        <v>2.42118068381502</v>
       </c>
       <c r="G11" s="1">
         <f>F11/2506*3500</f>
-        <v>1.94322451840339</v>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1557,24 +1536,24 @@
         <v>17</v>
       </c>
       <c r="B12" s="1">
-        <v>121.2010595</v>
+        <v>121.2000072</v>
       </c>
       <c r="C12" s="1">
-        <v>31.2964912</v>
+        <v>31.29804887</v>
       </c>
       <c r="D12" s="1">
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E12" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F12" s="1">
-        <f t="shared" ref="F12:F28" si="0">E12*34750*3500/116409</f>
-        <v>2.42118068381502</v>
+        <f>E12*34750*3500/116409</f>
+        <v>1.66940127767899</v>
       </c>
       <c r="G12" s="1">
-        <f t="shared" ref="G12:G28" si="1">F12/2506*3500</f>
-        <v>3.38153726789807</v>
+        <f>F12/2506*3500</f>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1582,24 +1561,24 @@
         <v>18</v>
       </c>
       <c r="B13" s="1">
-        <v>121.203164</v>
+        <v>121.2021117</v>
       </c>
       <c r="C13" s="1">
-        <v>31.2964912</v>
+        <v>31.29804887</v>
       </c>
       <c r="D13" s="1">
-        <v>3.38153726789807</v>
+        <v>1.94322451840339</v>
       </c>
       <c r="E13" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00133167948399901</v>
       </c>
       <c r="F13" s="1">
-        <f t="shared" si="0"/>
-        <v>2.42118068381502</v>
+        <f>E13*34750*3500/116409</f>
+        <v>1.39134875517683</v>
       </c>
       <c r="G13" s="1">
-        <f t="shared" si="1"/>
-        <v>3.38153726789807</v>
+        <f>F13/2506*3500</f>
+        <v>1.94322451840339</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1610,7 +1589,7 @@
         <v>121.1957982</v>
       </c>
       <c r="C14" s="1">
-        <v>31.29804887</v>
+        <v>31.25443412</v>
       </c>
       <c r="D14" s="1">
         <v>3.38153726789807</v>
@@ -1619,11 +1598,11 @@
         <v>0.00231734612310152</v>
       </c>
       <c r="F14" s="1">
-        <f t="shared" si="0"/>
+        <f>E14*34750*3500/116409</f>
         <v>2.42118068381502</v>
       </c>
       <c r="G14" s="1">
-        <f t="shared" si="1"/>
+        <f>F14/2506*3500</f>
         <v>3.38153726789807</v>
       </c>
     </row>
@@ -1632,24 +1611,24 @@
         <v>20</v>
       </c>
       <c r="B15" s="1">
-        <v>121.2000072</v>
+        <v>121.2021117</v>
       </c>
       <c r="C15" s="1">
-        <v>31.29804887</v>
+        <v>31.25443412</v>
       </c>
       <c r="D15" s="1">
-        <v>2.33156603027792</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E15" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F15" s="1">
-        <f t="shared" si="0"/>
-        <v>1.66940127767899</v>
+        <f>E15*34750*3500/116409</f>
+        <v>2.42118068381502</v>
       </c>
       <c r="G15" s="1">
-        <f t="shared" si="1"/>
-        <v>2.33156603027792</v>
+        <f>F15/2506*3500</f>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1657,24 +1636,24 @@
         <v>21</v>
       </c>
       <c r="B16" s="1">
-        <v>121.2021117</v>
+        <v>121.1926415</v>
       </c>
       <c r="C16" s="1">
-        <v>31.29804887</v>
+        <v>31.25599179</v>
       </c>
       <c r="D16" s="1">
-        <v>1.94322451840339</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E16" s="1">
-        <v>0.00133167948399901</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F16" s="1">
-        <f t="shared" si="0"/>
-        <v>1.39134875517683</v>
+        <f>E16*34750*3500/116409</f>
+        <v>1.66940127767899</v>
       </c>
       <c r="G16" s="1">
-        <f t="shared" si="1"/>
-        <v>1.94322451840339</v>
+        <f>F16/2506*3500</f>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1682,24 +1661,24 @@
         <v>22</v>
       </c>
       <c r="B17" s="1">
-        <v>121.1957982</v>
+        <v>121.198955</v>
       </c>
       <c r="C17" s="1">
-        <v>31.25443412</v>
+        <v>31.25599179</v>
       </c>
       <c r="D17" s="1">
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
       <c r="E17" s="1">
-        <v>0.00231734612310152</v>
+        <v>0.00159780746831107</v>
       </c>
       <c r="F17" s="1">
         <f>E17*34750*3500/116409</f>
-        <v>2.42118068381502</v>
+        <v>1.66940127767899</v>
       </c>
       <c r="G17" s="1">
         <f>F17/2506*3500</f>
-        <v>3.38153726789807</v>
+        <v>2.33156603027792</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1707,10 +1686,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="1">
-        <v>121.2021117</v>
+        <v>121.2000072</v>
       </c>
       <c r="C18" s="1">
-        <v>31.25443412</v>
+        <v>31.25754946</v>
       </c>
       <c r="D18" s="1">
         <v>3.38153726789807</v>
@@ -1732,24 +1711,24 @@
         <v>24</v>
       </c>
       <c r="B19" s="1">
-        <v>121.2042162</v>
+        <v>121.2147387</v>
       </c>
       <c r="C19" s="1">
-        <v>31.25443412</v>
+        <v>31.25754946</v>
       </c>
       <c r="D19" s="1">
-        <v>4.41705286278476</v>
+        <v>3.38153726789807</v>
       </c>
       <c r="E19" s="1">
-        <v>0.00302697841726619</v>
+        <v>0.00231734612310152</v>
       </c>
       <c r="F19" s="1">
         <f>E19*34750*3500/116409</f>
-        <v>3.16260984975389</v>
+        <v>2.42118068381502</v>
       </c>
       <c r="G19" s="1">
         <f>F19/2506*3500</f>
-        <v>4.41705286278476</v>
+        <v>3.38153726789807</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1757,200 +1736,34 @@
         <v>25</v>
       </c>
       <c r="B20" s="1">
-        <v>121.1926415</v>
+        <v>121.2010595</v>
       </c>
       <c r="C20" s="1">
-        <v>31.25599179</v>
+        <v>31.25910713</v>
       </c>
       <c r="D20" s="1">
-        <v>2.33156603027792</v>
+        <v>4.41705286278476</v>
       </c>
       <c r="E20" s="1">
-        <v>0.00159780746831107</v>
+        <v>0.00302697841726619</v>
       </c>
       <c r="F20" s="1">
         <f>E20*34750*3500/116409</f>
-        <v>1.66940127767899</v>
+        <v>3.16260984975389</v>
       </c>
       <c r="G20" s="1">
         <f>F20/2506*3500</f>
-        <v>2.33156603027792</v>
+        <v>4.41705286278476</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="1">
-        <v>121.198955</v>
-      </c>
-      <c r="C21" s="1">
-        <v>31.25599179</v>
-      </c>
-      <c r="D21" s="1">
-        <v>2.33156603027792</v>
-      </c>
-      <c r="E21" s="1">
-        <v>0.00159780746831107</v>
-      </c>
-      <c r="F21" s="1">
-        <f>E21*34750*3500/116409</f>
-        <v>1.66940127767899</v>
-      </c>
-      <c r="G21" s="1">
-        <f>F21/2506*3500</f>
-        <v>2.33156603027792</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1">
-        <v>121.2010595</v>
-      </c>
-      <c r="C22" s="1">
-        <v>31.25599179</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E22" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F22" s="1">
-        <f>E22*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G22" s="1">
-        <f>F22/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B23" s="1">
-        <v>121.2000072</v>
-      </c>
-      <c r="C23" s="1">
-        <v>31.25754946</v>
-      </c>
-      <c r="D23" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F23" s="1">
-        <f>E23*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G23" s="1">
-        <f>F23/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="1">
-        <v>121.2147387</v>
-      </c>
-      <c r="C24" s="1">
-        <v>31.25754946</v>
-      </c>
-      <c r="D24" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F24" s="1">
-        <f>E24*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G24" s="1">
-        <f>F24/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="1">
-        <v>121.1884325</v>
-      </c>
-      <c r="C25" s="1">
-        <v>31.25910713</v>
-      </c>
-      <c r="D25" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E25" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F25" s="1">
-        <f>E25*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G25" s="1">
-        <f>F25/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="1">
-        <v>121.2010595</v>
-      </c>
-      <c r="C26" s="1">
-        <v>31.25910713</v>
-      </c>
-      <c r="D26" s="1">
-        <v>4.41705286278476</v>
-      </c>
-      <c r="E26" s="1">
-        <v>0.00302697841726619</v>
-      </c>
-      <c r="F26" s="1">
-        <f>E26*34750*3500/116409</f>
-        <v>3.16260984975389</v>
-      </c>
-      <c r="G26" s="1">
-        <f>F26/2506*3500</f>
-        <v>4.41705286278476</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="1">
-        <v>121.203164</v>
-      </c>
-      <c r="C27" s="1">
-        <v>31.25910713</v>
-      </c>
-      <c r="D27" s="1">
-        <v>2.33156603027792</v>
-      </c>
-      <c r="E27" s="1">
-        <v>0.00159780746831107</v>
-      </c>
-      <c r="F27" s="1">
-        <f>E27*34750*3500/116409</f>
-        <v>1.66940127767899</v>
-      </c>
-      <c r="G27" s="1">
-        <f>F27/2506*3500</f>
-        <v>2.33156603027792</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/all_points_test.xlsx
+++ b/all_points_test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055"/>
+    <workbookView windowWidth="21094" windowHeight="9805"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <t>Gridid</t>
   </si>
@@ -50,61 +50,484 @@
     <t>totalDemandcal</t>
   </si>
   <si>
-    <t>[66, 29, -37]</t>
-  </si>
-  <si>
-    <t>[68, 30, -38]</t>
-  </si>
-  <si>
-    <t>[7, -2, -9]</t>
-  </si>
-  <si>
-    <t>[11, 0, -11]</t>
-  </si>
-  <si>
-    <t>[15, 2, -13]</t>
-  </si>
-  <si>
-    <t>[17, 3, -14]</t>
-  </si>
-  <si>
-    <t>[25, 7, -18]</t>
-  </si>
-  <si>
-    <t>[27, 8, -19]</t>
-  </si>
-  <si>
-    <t>[29, 9, -20]</t>
-  </si>
-  <si>
-    <t>[31, 10, -21]</t>
-  </si>
-  <si>
-    <t>[33, 11, -22]</t>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>[15, -4, -19]</t>
+  </si>
+  <si>
+    <t>[17, -3, -20]</t>
+  </si>
+  <si>
+    <t>[16, -5, -21]</t>
+  </si>
+  <si>
+    <t>[18, -4, -22]</t>
+  </si>
+  <si>
+    <t>[20, -3, -23]</t>
+  </si>
+  <si>
+    <t>[26, 0, -26]</t>
+  </si>
+  <si>
+    <t>[15, -7, -22]</t>
+  </si>
+  <si>
+    <t>[17, -6, -23]</t>
+  </si>
+  <si>
+    <t>[23, -3, -26]</t>
+  </si>
+  <si>
+    <t>[14, -9, -23]</t>
+  </si>
+  <si>
+    <t>[18, -7, -25]</t>
+  </si>
+  <si>
+    <t>[20, -6, -26]</t>
+  </si>
+  <si>
+    <t>[26, -3, -29]</t>
+  </si>
+  <si>
+    <t>[15, -10, -25]</t>
+  </si>
+  <si>
+    <t>[17, -9, -26]</t>
+  </si>
+  <si>
+    <t>[25, -5, -30]</t>
+  </si>
+  <si>
+    <t>[12, -13, -25]</t>
+  </si>
+  <si>
+    <t>[14, -12, -26]</t>
+  </si>
+  <si>
+    <t>[17, 6, -11]</t>
+  </si>
+  <si>
+    <t>[23, 9, -14]</t>
+  </si>
+  <si>
+    <t>[25, 10, -15]</t>
+  </si>
+  <si>
+    <t>[12, 2, -10]</t>
+  </si>
+  <si>
+    <t>[14, 3, -11]</t>
+  </si>
+  <si>
+    <t>[20, 6, -14]</t>
+  </si>
+  <si>
+    <t>[22, 7, -15]</t>
+  </si>
+  <si>
+    <t>[21, 5, -16]</t>
+  </si>
+  <si>
+    <t>[10, -2, -12]</t>
+  </si>
+  <si>
+    <t>[11, -3, -14]</t>
   </si>
   <si>
     <t>[35, 12, -23]</t>
   </si>
   <si>
-    <t>[39, 14, -25]</t>
-  </si>
-  <si>
-    <t>[41, 15, -26]</t>
-  </si>
-  <si>
-    <t>[47, 18, -29]</t>
-  </si>
-  <si>
-    <t>[49, 19, -30]</t>
-  </si>
-  <si>
-    <t>[53, 21, -32]</t>
-  </si>
-  <si>
-    <t>[55, 22, -33]</t>
-  </si>
-  <si>
-    <t>[59, 24, -35]</t>
+    <t>[43, 16, -27]</t>
+  </si>
+  <si>
+    <t>[36, 11, -25]</t>
+  </si>
+  <si>
+    <t>[31, 7, -24]</t>
+  </si>
+  <si>
+    <t>[33, 8, -25]</t>
+  </si>
+  <si>
+    <t>[35, 9, -26]</t>
+  </si>
+  <si>
+    <t>[32, 6, -26]</t>
+  </si>
+  <si>
+    <t>[36, 8, -28]</t>
+  </si>
+  <si>
+    <t>[38, 9, -29]</t>
+  </si>
+  <si>
+    <t>[40, 10, -30]</t>
+  </si>
+  <si>
+    <t>[35, 6, -29]</t>
+  </si>
+  <si>
+    <t>[37, 7, -30]</t>
+  </si>
+  <si>
+    <t>[39, 8, -31]</t>
+  </si>
+  <si>
+    <t>[36, 5, -31]</t>
+  </si>
+  <si>
+    <t>[38, 6, -32]</t>
+  </si>
+  <si>
+    <t>[42, 8, -34]</t>
+  </si>
+  <si>
+    <t>[60, 20, -40]</t>
+  </si>
+  <si>
+    <t>[55, 16, -39]</t>
+  </si>
+  <si>
+    <t>[57, 17, -40]</t>
+  </si>
+  <si>
+    <t>[65, 21, -44]</t>
+  </si>
+  <si>
+    <t>[56, 15, -41]</t>
+  </si>
+  <si>
+    <t>[58, 16, -42]</t>
+  </si>
+  <si>
+    <t>[62, 18, -44]</t>
+  </si>
+  <si>
+    <t>[64, 19, -45]</t>
+  </si>
+  <si>
+    <t>[57, 14, -43]</t>
+  </si>
+  <si>
+    <t>[59, 15, -44]</t>
+  </si>
+  <si>
+    <t>[61, 16, -45]</t>
+  </si>
+  <si>
+    <t>[63, 17, -46]</t>
+  </si>
+  <si>
+    <t>[60, 14, -46]</t>
+  </si>
+  <si>
+    <t>[62, 15, -47]</t>
+  </si>
+  <si>
+    <t>[64, 16, -48]</t>
+  </si>
+  <si>
+    <t>[66, 17, -49]</t>
+  </si>
+  <si>
+    <t>[63, 14, -49]</t>
+  </si>
+  <si>
+    <t>[65, 15, -50]</t>
+  </si>
+  <si>
+    <t>[58, 10, -48]</t>
+  </si>
+  <si>
+    <t>[62, 12, -50]</t>
+  </si>
+  <si>
+    <t>[59, 9, -50]</t>
+  </si>
+  <si>
+    <t>[63, 11, -52]</t>
+  </si>
+  <si>
+    <t>[65, 9, -56]</t>
+  </si>
+  <si>
+    <t>[53, 15, -38]</t>
+  </si>
+  <si>
+    <t>[52, 13, -39]</t>
+  </si>
+  <si>
+    <t>[54, 14, -40]</t>
+  </si>
+  <si>
+    <t>[51, 11, -40]</t>
+  </si>
+  <si>
+    <t>[53, 12, -41]</t>
+  </si>
+  <si>
+    <t>[42, 5, -37]</t>
+  </si>
+  <si>
+    <t>[43, 4, -39]</t>
+  </si>
+  <si>
+    <t>[45, 5, -40]</t>
+  </si>
+  <si>
+    <t>[47, 6, -41]</t>
+  </si>
+  <si>
+    <t>[54, 8, -46]</t>
+  </si>
+  <si>
+    <t>[22, 4, -18]</t>
+  </si>
+  <si>
+    <t>[24, 5, -19]</t>
+  </si>
+  <si>
+    <t>[28, 7, -21]</t>
+  </si>
+  <si>
+    <t>[30, 8, -22]</t>
+  </si>
+  <si>
+    <t>[17, 0, -17]</t>
+  </si>
+  <si>
+    <t>[23, 3, -20]</t>
+  </si>
+  <si>
+    <t>[25, 4, -21]</t>
+  </si>
+  <si>
+    <t>[14, -3, -17]</t>
+  </si>
+  <si>
+    <t>[22, 1, -21]</t>
+  </si>
+  <si>
+    <t>[26, 3, -23]</t>
+  </si>
+  <si>
+    <t>[23, 0, -23]</t>
+  </si>
+  <si>
+    <t>[25, 1, -24]</t>
+  </si>
+  <si>
+    <t>[27, 2, -25]</t>
+  </si>
+  <si>
+    <t>[13, -5, -18]</t>
+  </si>
+  <si>
+    <t>[12, -7, -19]</t>
+  </si>
+  <si>
+    <t>[14, -6, -20]</t>
+  </si>
+  <si>
+    <t>[11, -9, -20]</t>
+  </si>
+  <si>
+    <t>[12, -10, -22]</t>
+  </si>
+  <si>
+    <t>[7, -17, -24]</t>
+  </si>
+  <si>
+    <t>[9, -16, -25]</t>
+  </si>
+  <si>
+    <t>[26, -9, -35]</t>
+  </si>
+  <si>
+    <t>[68, 24, -44]</t>
+  </si>
+  <si>
+    <t>[70, 25, -45]</t>
+  </si>
+  <si>
+    <t>[67, 22, -45]</t>
+  </si>
+  <si>
+    <t>[69, 23, -46]</t>
+  </si>
+  <si>
+    <t>[71, 24, -47]</t>
+  </si>
+  <si>
+    <t>[66, 20, -46]</t>
+  </si>
+  <si>
+    <t>[68, 21, -47]</t>
+  </si>
+  <si>
+    <t>[70, 22, -48]</t>
+  </si>
+  <si>
+    <t>[72, 23, -49]</t>
+  </si>
+  <si>
+    <t>[74, 24, -50]</t>
+  </si>
+  <si>
+    <t>[65, 18, -47]</t>
+  </si>
+  <si>
+    <t>[67, 19, -48]</t>
+  </si>
+  <si>
+    <t>[69, 20, -49]</t>
+  </si>
+  <si>
+    <t>[71, 21, -50]</t>
+  </si>
+  <si>
+    <t>[68, 18, -50]</t>
+  </si>
+  <si>
+    <t>[70, 19, -51]</t>
+  </si>
+  <si>
+    <t>[72, 20, -52]</t>
+  </si>
+  <si>
+    <t>[76, 22, -54]</t>
+  </si>
+  <si>
+    <t>[78, 23, -55]</t>
+  </si>
+  <si>
+    <t>[69, 17, -52]</t>
+  </si>
+  <si>
+    <t>[71, 18, -53]</t>
+  </si>
+  <si>
+    <t>[73, 19, -54]</t>
+  </si>
+  <si>
+    <t>[79, 22, -57]</t>
+  </si>
+  <si>
+    <t>[81, 23, -58]</t>
+  </si>
+  <si>
+    <t>[72, 17, -55]</t>
+  </si>
+  <si>
+    <t>[74, 18, -56]</t>
+  </si>
+  <si>
+    <t>[76, 19, -57]</t>
+  </si>
+  <si>
+    <t>[78, 20, -58]</t>
+  </si>
+  <si>
+    <t>[82, 22, -60]</t>
+  </si>
+  <si>
+    <t>[29, 6, -23]</t>
+  </si>
+  <si>
+    <t>[30, 5, -25]</t>
+  </si>
+  <si>
+    <t>[29, 3, -26]</t>
+  </si>
+  <si>
+    <t>[31, 4, -27]</t>
+  </si>
+  <si>
+    <t>[33, 5, -28]</t>
+  </si>
+  <si>
+    <t>[32, 3, -29]</t>
+  </si>
+  <si>
+    <t>[34, 4, -30]</t>
+  </si>
+  <si>
+    <t>[29, 0, -29]</t>
+  </si>
+  <si>
+    <t>[31, 1, -30]</t>
+  </si>
+  <si>
+    <t>[33, 2, -31]</t>
+  </si>
+  <si>
+    <t>[35, 3, -32]</t>
+  </si>
+  <si>
+    <t>[32, 0, -32]</t>
+  </si>
+  <si>
+    <t>[34, 1, -33]</t>
+  </si>
+  <si>
+    <t>[33, -1, -34]</t>
+  </si>
+  <si>
+    <t>[49, 13, -36]</t>
+  </si>
+  <si>
+    <t>[51, 14, -37]</t>
+  </si>
+  <si>
+    <t>[44, 9, -35]</t>
+  </si>
+  <si>
+    <t>[50, 12, -38]</t>
+  </si>
+  <si>
+    <t>[43, 7, -36]</t>
+  </si>
+  <si>
+    <t>[45, 8, -37]</t>
+  </si>
+  <si>
+    <t>[47, 9, -38]</t>
+  </si>
+  <si>
+    <t>[44, 6, -38]</t>
+  </si>
+  <si>
+    <t>[46, 7, -39]</t>
+  </si>
+  <si>
+    <t>[48, 8, -40]</t>
+  </si>
+  <si>
+    <t>[85, 28, -57]</t>
+  </si>
+  <si>
+    <t>[87, 29, -58]</t>
+  </si>
+  <si>
+    <t>[86, 27, -59]</t>
+  </si>
+  <si>
+    <t>[88, 28, -60]</t>
+  </si>
+  <si>
+    <t>[85, 25, -60]</t>
+  </si>
+  <si>
+    <t>[93, 29, -64]</t>
+  </si>
+  <si>
+    <t>[84, 23, -61]</t>
+  </si>
+  <si>
+    <t>[90, 26, -64]</t>
   </si>
 </sst>
 </file>
@@ -1252,20 +1675,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="8.72566371681416" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H160"/>
+  <sheetFormatPr defaultColWidth="8.72972972972973" defaultRowHeight="14.1" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="7" width="12.7964601769912"/>
+    <col min="2" max="7" width="12.7927927927928"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1274,498 +1697,4154 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C2" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D2">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E2">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F2">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G2">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C3" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D3">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E3">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F3">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G3">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C4" s="1">
+        <v>31.26689547</v>
+      </c>
+      <c r="D4">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E4">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F4">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G4">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C5" s="1">
+        <v>31.27001081</v>
+      </c>
+      <c r="D5">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E5">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F5">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G5">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C6" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D6">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E6">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F6">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G6">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C7" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D7">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E7">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F7">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G7">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C8" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D8">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E8">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F8">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G8">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C9" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D9">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E9">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F9">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G9">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C10" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D10">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E10">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F10">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G10">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1">
+        <v>121.198955</v>
+      </c>
+      <c r="C11" s="1">
+        <v>31.26845314</v>
+      </c>
+      <c r="D11">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E11">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F11">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G11">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1">
+        <v>121.198955</v>
+      </c>
+      <c r="C12" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D12">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E12">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F12">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G12">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1">
+        <v>121.198955</v>
+      </c>
+      <c r="C13" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D13">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E13">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F13">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G13">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1">
+        <v>121.198955</v>
+      </c>
+      <c r="C14" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D14">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E14">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F14">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G14">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1">
+        <v>121.203164</v>
+      </c>
+      <c r="C15" s="1">
+        <v>31.2964912</v>
+      </c>
+      <c r="D15">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E15">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F15">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G15">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1">
+        <v>121.2042162</v>
+      </c>
+      <c r="C16" s="1">
+        <v>31.25443412</v>
+      </c>
+      <c r="D16">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E16">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F16">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G16">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1">
+        <v>121.2042162</v>
+      </c>
+      <c r="C17" s="1">
+        <v>31.2606648</v>
+      </c>
+      <c r="D17">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E17">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F17">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G17">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1">
+        <v>121.207373</v>
+      </c>
+      <c r="C18" s="1">
+        <v>31.25910713</v>
+      </c>
+      <c r="D18">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E18">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F18">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G18">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1">
+        <v>121.207373</v>
+      </c>
+      <c r="C19" s="1">
+        <v>31.26845314</v>
+      </c>
+      <c r="D19">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="E19">
+        <v>0.00126692492160118</v>
+      </c>
+      <c r="F19">
+        <v>1.32369270064809</v>
+      </c>
+      <c r="G19">
+        <v>1.8487328221342</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1">
+        <v>121.1831712</v>
+      </c>
+      <c r="C20" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D20">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E20">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F20">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G20">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1">
+        <v>121.1831712</v>
+      </c>
+      <c r="C21" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D21">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E21">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F21">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G21">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1">
+        <v>121.1842235</v>
+      </c>
+      <c r="C22" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D22">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E22">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F22">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G22">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1">
+        <v>121.1842235</v>
+      </c>
+      <c r="C23" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D23">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E23">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F23">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G23">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1">
+        <v>121.1852757</v>
+      </c>
+      <c r="C24" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D24">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E24">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F24">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G24">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1">
+        <v>121.1852757</v>
+      </c>
+      <c r="C25" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D25">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E25">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F25">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G25">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1">
+        <v>121.1852757</v>
+      </c>
+      <c r="C26" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D26">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E26">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F26">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G26">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1">
+        <v>121.1852757</v>
+      </c>
+      <c r="C27" s="1">
+        <v>31.28870285</v>
+      </c>
+      <c r="D27">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E27">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F27">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G27">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1">
+        <v>121.186328</v>
+      </c>
+      <c r="C28" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D28">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E28">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F28">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G28">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C29" s="1">
+        <v>31.25910713</v>
+      </c>
+      <c r="D29">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="E29">
+        <v>0.00133167948399901</v>
+      </c>
+      <c r="F29">
+        <v>1.39134875517683</v>
+      </c>
+      <c r="G29">
+        <v>1.94322451840339</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1">
+        <v>121.186328</v>
+      </c>
+      <c r="C30" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D30">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E30">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F30">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G30">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1">
+        <v>121.186328</v>
+      </c>
+      <c r="C31" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D31">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E31">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F31">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G31">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1">
+        <v>121.1873802</v>
+      </c>
+      <c r="C32" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D32">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E32">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F32">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G32">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C33" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D33">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E33">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F33">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G33">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C34" s="1">
+        <v>31.29026052</v>
+      </c>
+      <c r="D34">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E34">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F34">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G34">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C35" s="1">
+        <v>31.2606648</v>
+      </c>
+      <c r="D35">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E35">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F35">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G35">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C36" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D36">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E36">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F36">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G36">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C37" s="1">
+        <v>31.28870285</v>
+      </c>
+      <c r="D37">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E37">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F37">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G37">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C38" s="1">
+        <v>31.25599179</v>
+      </c>
+      <c r="D38">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E38">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F38">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G38">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C39" s="1">
+        <v>31.2653378</v>
+      </c>
+      <c r="D39">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E39">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F39">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G39">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C40" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D40">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E40">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F40">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G40">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C41" s="1">
+        <v>31.28870285</v>
+      </c>
+      <c r="D41">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E41">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F41">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G41">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C42" s="1">
+        <v>31.25599179</v>
+      </c>
+      <c r="D42">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E42">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F42">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G42">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C43" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D43">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E43">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F43">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G43">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C44" s="1">
+        <v>31.28870285</v>
+      </c>
+      <c r="D44">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E44">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F44">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G44">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C45" s="1">
+        <v>31.29181819</v>
+      </c>
+      <c r="D45">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="E45">
+        <v>0.00159780746831107</v>
+      </c>
+      <c r="F45">
+        <v>1.66940127767899</v>
+      </c>
+      <c r="G45">
+        <v>2.33156603027792</v>
+      </c>
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C46" s="1">
+        <v>31.26845314</v>
+      </c>
+      <c r="D46">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E46">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F46">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G46">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C47" s="1">
+        <v>31.27156848</v>
+      </c>
+      <c r="D47">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E47">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F47">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G47">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C48" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D48">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E48">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F48">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G48">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C49" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D49">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E49">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F49">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G49">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1">
         <v>121.194746</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C50" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D50">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E50">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F50">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G50">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1">
+        <v>121.194746</v>
+      </c>
+      <c r="C51" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D51">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E51">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F51">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G51">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1">
+        <v>121.194746</v>
+      </c>
+      <c r="C52" s="1">
         <v>31.29026052</v>
       </c>
-      <c r="D2" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F2" s="1">
-        <f>E2*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G2" s="1">
-        <f>F2/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="D52">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E52">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F52">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G52">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C53" s="1">
+        <v>31.25443412</v>
+      </c>
+      <c r="D53">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E53">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F53">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G53">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C54" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D54">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E54">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F54">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G54">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C55" s="1">
+        <v>31.29337586</v>
+      </c>
+      <c r="D55">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E55">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F55">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G55">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C56" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D56">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E56">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F56">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G56">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C57" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D57">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E57">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F57">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G57">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1">
+        <v>121.2010595</v>
+      </c>
+      <c r="C58" s="1">
+        <v>31.29337586</v>
+      </c>
+      <c r="D58">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E58">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F58">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G58">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1">
+        <v>121.2010595</v>
+      </c>
+      <c r="C59" s="1">
+        <v>31.2964912</v>
+      </c>
+      <c r="D59">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E59">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F59">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G59">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C60" s="1">
+        <v>31.25443412</v>
+      </c>
+      <c r="D60">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E60">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F60">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G60">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H60" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C61" s="1">
+        <v>31.2606648</v>
+      </c>
+      <c r="D61">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E61">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F61">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G61">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H61" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1">
         <v>121.2052685</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C62" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D62">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E62">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F62">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G62">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H62" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1">
+        <v>121.2052685</v>
+      </c>
+      <c r="C63" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D63">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E63">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F63">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G63">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H63" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1">
+        <v>121.2084252</v>
+      </c>
+      <c r="C64" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D64">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E64">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F64">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G64">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1">
+        <v>121.2084252</v>
+      </c>
+      <c r="C65" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D65">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E65">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F65">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G65">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1">
+        <v>121.2126342</v>
+      </c>
+      <c r="C66" s="1">
+        <v>31.2606648</v>
+      </c>
+      <c r="D66">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E66">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F66">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G66">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1">
+        <v>121.2126342</v>
+      </c>
+      <c r="C67" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D67">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E67">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F67">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G67">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1">
+        <v>121.22</v>
+      </c>
+      <c r="C68" s="1">
+        <v>31.26222246</v>
+      </c>
+      <c r="D68">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="E68">
+        <v>0.00167952910398954</v>
+      </c>
+      <c r="F68">
+        <v>1.75478465816842</v>
+      </c>
+      <c r="G68">
+        <v>2.45081656168774</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C69" s="1">
+        <v>31.26845314</v>
+      </c>
+      <c r="D69">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E69">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F69">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G69">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1">
+        <v>121.194746</v>
+      </c>
+      <c r="C70" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D70">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E70">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F70">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G70">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1">
+        <v>121.194746</v>
+      </c>
+      <c r="C71" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D71">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E71">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F71">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G71">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C72" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D72">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E72">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F72">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G72">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H72" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C73" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D73">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E73">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F73">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G73">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H73" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1">
+        <v>121.2000072</v>
+      </c>
+      <c r="C74" s="1">
+        <v>31.29804887</v>
+      </c>
+      <c r="D74">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E74">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F74">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G74">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H74" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1">
+        <v>121.2052685</v>
+      </c>
+      <c r="C75" s="1">
+        <v>31.26222246</v>
+      </c>
+      <c r="D75">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E75">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F75">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G75">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1">
+        <v>121.2052685</v>
+      </c>
+      <c r="C76" s="1">
+        <v>31.2653378</v>
+      </c>
+      <c r="D76">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E76">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F76">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G76">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1">
+        <v>121.2052685</v>
+      </c>
+      <c r="C77" s="1">
+        <v>31.26845314</v>
+      </c>
+      <c r="D77">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E77">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F77">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G77">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1">
+        <v>121.2084252</v>
+      </c>
+      <c r="C78" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D78">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="E78">
+        <v>0.00173257256263954</v>
+      </c>
+      <c r="F78">
+        <v>1.81020486329265</v>
+      </c>
+      <c r="G78">
+        <v>2.52821908281096</v>
+      </c>
+      <c r="H78" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1">
+        <v>121.186328</v>
+      </c>
+      <c r="C79" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D79">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E79">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F79">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G79">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H79" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1">
+        <v>121.1873802</v>
+      </c>
+      <c r="C80" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D80">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E80">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F80">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G80">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H80" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1">
+        <v>121.1873802</v>
+      </c>
+      <c r="C81" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D81">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E81">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F81">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G81">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H81" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1">
+        <v>121.1873802</v>
+      </c>
+      <c r="C82" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D82">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E82">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F82">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G82">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H82" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C83" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D83">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E83">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F83">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G83">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C84" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D84">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E84">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F84">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G84">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H84" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C85" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D85">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E85">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F85">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G85">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H85" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C86" s="1">
+        <v>31.26689547</v>
+      </c>
+      <c r="D86">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E86">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F86">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G86">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C87" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D87">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E87">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F87">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G87">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C88" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D88">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E88">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F88">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G88">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C89" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D89">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E89">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F89">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G89">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C90" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D90">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E90">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F90">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G90">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H90" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C91" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D91">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="E91">
+        <v>0.00231734612310152</v>
+      </c>
+      <c r="F91">
+        <v>2.42118068381502</v>
+      </c>
+      <c r="G91">
+        <v>3.38153726789807</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C92" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D92">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E92">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F92">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G92">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C93" s="1">
         <v>31.29026052</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F3" s="1">
-        <f>E3*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G3" s="1">
-        <f>F3/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1">
+      <c r="D93">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E93">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F93">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G93">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C94" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D94">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E94">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F94">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G94">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H94" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="1">
         <v>121.1957982</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C95" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D95">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E95">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F95">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G95">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H95" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="1">
+        <v>121.198955</v>
+      </c>
+      <c r="C96" s="1">
+        <v>31.2653378</v>
+      </c>
+      <c r="D96">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E96">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F96">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G96">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="1">
+        <v>121.2105297</v>
+      </c>
+      <c r="C97" s="1">
+        <v>31.2606648</v>
+      </c>
+      <c r="D97">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E97">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F97">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G97">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H97" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="1">
+        <v>121.2105297</v>
+      </c>
+      <c r="C98" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D98">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E98">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F98">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G98">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="1">
+        <v>121.2147387</v>
+      </c>
+      <c r="C99" s="1">
+        <v>31.25754946</v>
+      </c>
+      <c r="D99">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="E99">
+        <v>0.00262453328476459</v>
+      </c>
+      <c r="F99">
+        <v>2.74213214407385</v>
+      </c>
+      <c r="G99">
+        <v>3.82979349730985</v>
+      </c>
+      <c r="H99" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C100" s="1">
+        <v>31.27156848</v>
+      </c>
+      <c r="D100">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E100">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F100">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G100">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="1">
+        <v>121.190537</v>
+      </c>
+      <c r="C101" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D101">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E101">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F101">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G101">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C102" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D102">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E102">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F102">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G102">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C103" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D103">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E103">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F103">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G103">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C104" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D104">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E104">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F104">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G104">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C105" s="1">
+        <v>31.2606648</v>
+      </c>
+      <c r="D105">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E105">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F105">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G105">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H105" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C106" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D106">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E106">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F106">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G106">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C107" s="1">
+        <v>31.26689547</v>
+      </c>
+      <c r="D107">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E107">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F107">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G107">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H107" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8">
+      <c r="A108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C108" s="1">
+        <v>31.27001081</v>
+      </c>
+      <c r="D108">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E108">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F108">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G108">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
+      <c r="A109" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C109" s="1">
+        <v>31.27312615</v>
+      </c>
+      <c r="D109">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E109">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F109">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G109">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H109" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8">
+      <c r="A110" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C110" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D110">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E110">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F110">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G110">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H110" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8">
+      <c r="A111" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C111" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D111">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E111">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F111">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G111">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H111" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8">
+      <c r="A112" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C112" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D112">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E112">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F112">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G112">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
+      <c r="A113" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C113" s="1">
         <v>31.29181819</v>
       </c>
-      <c r="D4" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F4" s="1">
-        <f>E4*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G4" s="1">
-        <f>F4/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1">
+      <c r="D113">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E113">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F113">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G113">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H113" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8">
+      <c r="A114" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C114" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D114">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E114">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F114">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G114">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
+      <c r="A115" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C115" s="1">
+        <v>31.26689547</v>
+      </c>
+      <c r="D115">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E115">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F115">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G115">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H115" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8">
+      <c r="A116" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C116" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D116">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E116">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F116">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G116">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H116" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8">
+      <c r="A117" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C117" s="1">
+        <v>31.29493353</v>
+      </c>
+      <c r="D117">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E117">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F117">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G117">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8">
+      <c r="A118" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="1">
+        <v>121.2021117</v>
+      </c>
+      <c r="C118" s="1">
+        <v>31.29804887</v>
+      </c>
+      <c r="D118">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E118">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F118">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G118">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8">
+      <c r="A119" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="1">
+        <v>121.2052685</v>
+      </c>
+      <c r="C119" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D119">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E119">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F119">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G119">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8">
+      <c r="A120" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="1">
+        <v>121.2052685</v>
+      </c>
+      <c r="C120" s="1">
+        <v>31.29026052</v>
+      </c>
+      <c r="D120">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E120">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F120">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G120">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H120" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8">
+      <c r="A121" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="1">
         <v>121.2063207</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C121" s="1">
+        <v>31.26378013</v>
+      </c>
+      <c r="D121">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E121">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F121">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G121">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8">
+      <c r="A122" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="1">
+        <v>121.2063207</v>
+      </c>
+      <c r="C122" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D122">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E122">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F122">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G122">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H122" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
+      <c r="A123" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="1">
+        <v>121.2063207</v>
+      </c>
+      <c r="C123" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D123">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E123">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F123">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G123">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H123" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8">
+      <c r="A124" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="1">
+        <v>121.2084252</v>
+      </c>
+      <c r="C124" s="1">
+        <v>31.29493353</v>
+      </c>
+      <c r="D124">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E124">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F124">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G124">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
+      <c r="A125" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="1">
+        <v>121.2094775</v>
+      </c>
+      <c r="C125" s="1">
+        <v>31.25910713</v>
+      </c>
+      <c r="D125">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E125">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F125">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G125">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H125" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8">
+      <c r="A126" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="1">
+        <v>121.2094775</v>
+      </c>
+      <c r="C126" s="1">
+        <v>31.26222246</v>
+      </c>
+      <c r="D126">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E126">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F126">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G126">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H126" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8">
+      <c r="A127" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="1">
+        <v>121.2094775</v>
+      </c>
+      <c r="C127" s="1">
+        <v>31.26845314</v>
+      </c>
+      <c r="D127">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E127">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F127">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G127">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H127" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
+      <c r="A128" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="1">
+        <v>121.2094775</v>
+      </c>
+      <c r="C128" s="1">
+        <v>31.27156848</v>
+      </c>
+      <c r="D128">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="E128">
+        <v>0.00296930455635492</v>
+      </c>
+      <c r="F128">
+        <v>3.1023517654706</v>
+      </c>
+      <c r="G128">
+        <v>4.33289352719358</v>
+      </c>
+      <c r="H128" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8">
+      <c r="A129" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="1">
+        <v>121.1884325</v>
+      </c>
+      <c r="C129" s="1">
+        <v>31.28402984</v>
+      </c>
+      <c r="D129">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E129">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F129">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G129">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H129" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8">
+      <c r="A130" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="1">
+        <v>121.1894847</v>
+      </c>
+      <c r="C130" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D130">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E130">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F130">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G130">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8">
+      <c r="A131" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C131" s="1">
+        <v>31.27624149</v>
+      </c>
+      <c r="D131">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E131">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F131">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G131">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
+      <c r="A132" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C132" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D132">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E132">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F132">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G132">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H132" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8">
+      <c r="A133" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="1">
+        <v>121.1915892</v>
+      </c>
+      <c r="C133" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D133">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E133">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F133">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G133">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H133" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8">
+      <c r="A134" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C134" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D134">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E134">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F134">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G134">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H134" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8">
+      <c r="A135" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="1">
+        <v>121.1936937</v>
+      </c>
+      <c r="C135" s="1">
+        <v>31.28247217</v>
+      </c>
+      <c r="D135">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E135">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F135">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G135">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H135" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
+      <c r="A136" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C136" s="1">
+        <v>31.28870285</v>
+      </c>
+      <c r="D136">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E136">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F136">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G136">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H136" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8">
+      <c r="A137" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C137" s="1">
         <v>31.29181819</v>
       </c>
-      <c r="D5" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F5" s="1">
-        <f>E5*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G5" s="1">
-        <f>F5/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="D137">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E137">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F137">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G137">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8">
+      <c r="A138" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="1">
+        <v>121.1957982</v>
+      </c>
+      <c r="C138" s="1">
+        <v>31.29804887</v>
+      </c>
+      <c r="D138">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E138">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F138">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G138">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8">
+      <c r="A139" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C139" s="1">
+        <v>31.2653378</v>
+      </c>
+      <c r="D139">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E139">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F139">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G139">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H139" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
+      <c r="A140" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="1">
         <v>121.198955</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C140" s="1">
         <v>31.29337586</v>
       </c>
-      <c r="D6" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F6" s="1">
-        <f>E6*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G6" s="1">
-        <f>F6/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1">
+      <c r="D140">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E140">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F140">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G140">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H140" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8">
+      <c r="A141" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" s="1">
+        <v>121.2000072</v>
+      </c>
+      <c r="C141" s="1">
+        <v>31.25754946</v>
+      </c>
+      <c r="D141">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E141">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F141">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G141">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H141" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8">
+      <c r="A142" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" s="1">
+        <v>121.2042162</v>
+      </c>
+      <c r="C142" s="1">
+        <v>31.27935683</v>
+      </c>
+      <c r="D142">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="E142">
+        <v>0.00302697841726619</v>
+      </c>
+      <c r="F142">
+        <v>3.16260984975389</v>
+      </c>
+      <c r="G142">
+        <v>4.41705286278476</v>
+      </c>
+      <c r="H142" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
+      <c r="A143" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C143" s="1">
+        <v>31.26222246</v>
+      </c>
+      <c r="D143">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E143">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F143">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G143">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H143" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8">
+      <c r="A144" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B144" s="1">
+        <v>121.1926415</v>
+      </c>
+      <c r="C144" s="1">
+        <v>31.2653378</v>
+      </c>
+      <c r="D144">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E144">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F144">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G144">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H144" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
+      <c r="A145" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" s="1">
+        <v>121.194746</v>
+      </c>
+      <c r="C145" s="1">
+        <v>31.2653378</v>
+      </c>
+      <c r="D145">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E145">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F145">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G145">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H145" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8">
+      <c r="A146" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" s="1">
+        <v>121.194746</v>
+      </c>
+      <c r="C146" s="1">
+        <v>31.27156848</v>
+      </c>
+      <c r="D146">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E146">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F146">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G146">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H146" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
+      <c r="A147" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C147" s="1">
+        <v>31.27156848</v>
+      </c>
+      <c r="D147">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E147">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F147">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G147">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H147" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8">
+      <c r="A148" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C148" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D148">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E148">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F148">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G148">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H148" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8">
+      <c r="A149" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" s="1">
+        <v>121.1968505</v>
+      </c>
+      <c r="C149" s="1">
+        <v>31.27779916</v>
+      </c>
+      <c r="D149">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E149">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F149">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G149">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H149" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8">
+      <c r="A150" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" s="1">
         <v>121.2010595</v>
       </c>
-      <c r="C7" s="1">
-        <v>31.29337586</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F7" s="1">
-        <f>E7*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G7" s="1">
-        <f>F7/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="1">
-        <v>121.2084252</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="C150" s="1">
+        <v>31.25599179</v>
+      </c>
+      <c r="D150">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E150">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F150">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G150">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H150" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8">
+      <c r="A151" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" s="1">
+        <v>121.2010595</v>
+      </c>
+      <c r="C151" s="1">
+        <v>31.25910713</v>
+      </c>
+      <c r="D151">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E151">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F151">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G151">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H151" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8">
+      <c r="A152" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" s="1">
+        <v>121.2010595</v>
+      </c>
+      <c r="C152" s="1">
+        <v>31.26222246</v>
+      </c>
+      <c r="D152">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="E152">
+        <v>0.00316683795820486</v>
+      </c>
+      <c r="F152">
+        <v>3.30873615155758</v>
+      </c>
+      <c r="G152">
+        <v>4.62113987647706</v>
+      </c>
+      <c r="H152" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8">
+      <c r="A153" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" s="1">
+        <v>121.1979027</v>
+      </c>
+      <c r="C153" s="1">
         <v>31.29493353</v>
       </c>
-      <c r="D8" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F8" s="1">
-        <f>E8*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G8" s="1">
-        <f>F8/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1">
-        <v>121.2010595</v>
-      </c>
-      <c r="C9" s="1">
-        <v>31.2964912</v>
-      </c>
-      <c r="D9" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F9" s="1">
-        <f>E9*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G9" s="1">
-        <f>F9/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="1">
+      <c r="D153">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E153">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F153">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G153">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H153" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
+      <c r="A154" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" s="1">
+        <v>121.198955</v>
+      </c>
+      <c r="C154" s="1">
+        <v>31.25599179</v>
+      </c>
+      <c r="D154">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E154">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F154">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G154">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H154" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8">
+      <c r="A155" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" s="1">
         <v>121.203164</v>
       </c>
-      <c r="C10" s="1">
-        <v>31.2964912</v>
-      </c>
-      <c r="D10" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F10" s="1">
-        <f>E10*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G10" s="1">
-        <f>F10/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1">
-        <v>121.1957982</v>
-      </c>
-      <c r="C11" s="1">
-        <v>31.29804887</v>
-      </c>
-      <c r="D11" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E11" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F11" s="1">
-        <f>E11*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G11" s="1">
-        <f>F11/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="1">
-        <v>121.2000072</v>
-      </c>
-      <c r="C12" s="1">
-        <v>31.29804887</v>
-      </c>
-      <c r="D12" s="1">
-        <v>2.33156603027792</v>
-      </c>
-      <c r="E12" s="1">
-        <v>0.00159780746831107</v>
-      </c>
-      <c r="F12" s="1">
-        <f>E12*34750*3500/116409</f>
-        <v>1.66940127767899</v>
-      </c>
-      <c r="G12" s="1">
-        <f>F12/2506*3500</f>
-        <v>2.33156603027792</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1">
-        <v>121.2021117</v>
-      </c>
-      <c r="C13" s="1">
-        <v>31.29804887</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1.94322451840339</v>
-      </c>
-      <c r="E13" s="1">
-        <v>0.00133167948399901</v>
-      </c>
-      <c r="F13" s="1">
-        <f>E13*34750*3500/116409</f>
-        <v>1.39134875517683</v>
-      </c>
-      <c r="G13" s="1">
-        <f>F13/2506*3500</f>
-        <v>1.94322451840339</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1">
-        <v>121.1957982</v>
-      </c>
-      <c r="C14" s="1">
-        <v>31.25443412</v>
-      </c>
-      <c r="D14" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E14" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F14" s="1">
-        <f>E14*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G14" s="1">
-        <f>F14/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1">
-        <v>121.2021117</v>
-      </c>
-      <c r="C15" s="1">
-        <v>31.25443412</v>
-      </c>
-      <c r="D15" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F15" s="1">
-        <f>E15*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G15" s="1">
-        <f>F15/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="1">
-        <v>121.1926415</v>
-      </c>
-      <c r="C16" s="1">
-        <v>31.25599179</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2.33156603027792</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0.00159780746831107</v>
-      </c>
-      <c r="F16" s="1">
-        <f>E16*34750*3500/116409</f>
-        <v>1.66940127767899</v>
-      </c>
-      <c r="G16" s="1">
-        <f>F16/2506*3500</f>
-        <v>2.33156603027792</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="1">
-        <v>121.198955</v>
-      </c>
-      <c r="C17" s="1">
-        <v>31.25599179</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2.33156603027792</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0.00159780746831107</v>
-      </c>
-      <c r="F17" s="1">
-        <f>E17*34750*3500/116409</f>
-        <v>1.66940127767899</v>
-      </c>
-      <c r="G17" s="1">
-        <f>F17/2506*3500</f>
-        <v>2.33156603027792</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="1">
-        <v>121.2000072</v>
-      </c>
-      <c r="C18" s="1">
-        <v>31.25754946</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F18" s="1">
-        <f>E18*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G18" s="1">
-        <f>F18/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="1">
-        <v>121.2147387</v>
-      </c>
-      <c r="C19" s="1">
-        <v>31.25754946</v>
-      </c>
-      <c r="D19" s="1">
-        <v>3.38153726789807</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.00231734612310152</v>
-      </c>
-      <c r="F19" s="1">
-        <f>E19*34750*3500/116409</f>
-        <v>2.42118068381502</v>
-      </c>
-      <c r="G19" s="1">
-        <f>F19/2506*3500</f>
-        <v>3.38153726789807</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1">
-        <v>121.2010595</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="C155" s="1">
         <v>31.25910713</v>
       </c>
-      <c r="D20" s="1">
-        <v>4.41705286278476</v>
-      </c>
-      <c r="E20" s="1">
-        <v>0.00302697841726619</v>
-      </c>
-      <c r="F20" s="1">
-        <f>E20*34750*3500/116409</f>
-        <v>3.16260984975389</v>
-      </c>
-      <c r="G20" s="1">
-        <f>F20/2506*3500</f>
-        <v>4.41705286278476</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
+      <c r="D155">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E155">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F155">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G155">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H155" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8">
+      <c r="A156" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" s="1">
+        <v>121.203164</v>
+      </c>
+      <c r="C156" s="1">
+        <v>31.28714518</v>
+      </c>
+      <c r="D156">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E156">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F156">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G156">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H156" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
+      <c r="A157" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" s="1">
+        <v>121.2063207</v>
+      </c>
+      <c r="C157" s="1">
+        <v>31.28558751</v>
+      </c>
+      <c r="D157">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E157">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F157">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G157">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H157" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8">
+      <c r="A158" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" s="1">
+        <v>121.2063207</v>
+      </c>
+      <c r="C158" s="1">
+        <v>31.29181819</v>
+      </c>
+      <c r="D158">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E158">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F158">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G158">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H158" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8">
+      <c r="A159" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" s="1">
+        <v>121.2094775</v>
+      </c>
+      <c r="C159" s="1">
+        <v>31.27468382</v>
+      </c>
+      <c r="D159">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E159">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F159">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G159">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H159" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
+      <c r="A160" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="1">
+        <v>121.2094775</v>
+      </c>
+      <c r="C160" s="1">
+        <v>31.2809145</v>
+      </c>
+      <c r="D160">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="E160">
+        <v>0.0037247740269323</v>
+      </c>
+      <c r="F160">
+        <v>3.891671958574</v>
+      </c>
+      <c r="G160">
+        <v>5.43529603152794</v>
+      </c>
+      <c r="H160" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="A2:H180">
+    <sortCondition ref="G2"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
